--- a/yellow-server/data/uploads/场所人员名单1.xlsx
+++ b/yellow-server/data/uploads/场所人员名单1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workprogram\扫黄\扫黄\代码\antiporn\上传模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2B6715-7525-4FDC-98F0-833E5A38D8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E29D6E-978B-4399-B18A-172D125D0DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,64 +90,66 @@
     <t>张三</t>
   </si>
   <si>
+    <t>老王</t>
+  </si>
+  <si>
+    <t>310227199002301002</t>
+  </si>
+  <si>
+    <t>老张</t>
+  </si>
+  <si>
+    <t>老李</t>
+  </si>
+  <si>
+    <t>310227199002301004</t>
+  </si>
+  <si>
+    <t>小王</t>
+  </si>
+  <si>
+    <t>310227199002301005</t>
+  </si>
+  <si>
+    <t>小李</t>
+  </si>
+  <si>
+    <t>310227199002301006</t>
+  </si>
+  <si>
+    <t>小胡</t>
+  </si>
+  <si>
+    <t>310227199002301007</t>
+  </si>
+  <si>
+    <t>小刚</t>
+  </si>
+  <si>
+    <t>310227199002301008</t>
+  </si>
+  <si>
+    <t>小金</t>
+  </si>
+  <si>
+    <t>310227199002301009</t>
+  </si>
+  <si>
+    <t>小钱</t>
+  </si>
+  <si>
+    <t>310227199002301010</t>
+  </si>
+  <si>
+    <t>手机号码</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>310227199002301001</t>
-  </si>
-  <si>
-    <t>老王</t>
-  </si>
-  <si>
-    <t>310227199002301002</t>
-  </si>
-  <si>
-    <t>老张</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>310227199002301003</t>
-  </si>
-  <si>
-    <t>老李</t>
-  </si>
-  <si>
-    <t>310227199002301004</t>
-  </si>
-  <si>
-    <t>小王</t>
-  </si>
-  <si>
-    <t>310227199002301005</t>
-  </si>
-  <si>
-    <t>小李</t>
-  </si>
-  <si>
-    <t>310227199002301006</t>
-  </si>
-  <si>
-    <t>小胡</t>
-  </si>
-  <si>
-    <t>310227199002301007</t>
-  </si>
-  <si>
-    <t>小刚</t>
-  </si>
-  <si>
-    <t>310227199002301008</t>
-  </si>
-  <si>
-    <t>小金</t>
-  </si>
-  <si>
-    <t>310227199002301009</t>
-  </si>
-  <si>
-    <t>小钱</t>
-  </si>
-  <si>
-    <t>310227199002301010</t>
-  </si>
-  <si>
-    <t>手机号码</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -212,7 +214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -226,6 +228,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -538,7 +543,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
@@ -560,8 +565,8 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
+      <c r="G2" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="H2" s="4">
         <v>13824163758</v>
@@ -584,10 +589,10 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="H3" s="4">
         <v>15932048176</v>
@@ -610,10 +615,10 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="H4" s="4">
         <v>18851496203</v>
@@ -636,10 +641,10 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H5" s="4">
         <v>19108374529</v>
@@ -662,10 +667,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H6" s="4">
         <v>13760853924</v>
@@ -688,10 +693,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H7" s="4">
         <v>15507468291</v>
@@ -714,10 +719,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H8" s="4">
         <v>18936274085</v>
@@ -740,10 +745,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H9" s="4">
         <v>19827365041</v>
@@ -766,10 +771,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H10" s="4">
         <v>13650942817</v>
@@ -792,10 +797,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H11" s="4">
         <v>15286493075</v>
